--- a/dist/勤務シフト生成システム/勤務条件表_ひな形.xlsx
+++ b/dist/勤務シフト生成システム/勤務条件表_ひな形.xlsx
@@ -1714,7 +1714,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>HARD1</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH1</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH2</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH3</t>
         </is>
       </c>
     </row>
